--- a/01-your-first-py-cell.xlsx
+++ b/01-your-first-py-cell.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="23">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -99,8 +99,69 @@
       <color rgb="002E7D2E"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002A4365"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00718096"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00718096"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002A4365"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00C53030"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="002F6E2F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -137,8 +198,38 @@
         <bgColor rgb="00E6F3E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A4365"/>
+        <bgColor rgb="002A4365"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1EFE8"/>
+        <bgColor rgb="00F1EFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF0F5"/>
+        <bgColor rgb="00EDF0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7E7"/>
+        <bgColor rgb="00FCE7E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7F1E7"/>
+        <bgColor rgb="00E7F1E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -202,11 +293,68 @@
         <color rgb="002E7D2E"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D8DAE0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D8DAE0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8DAE0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8DAE0"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <left style="medium">
+        <color rgb="00C53030"/>
+      </left>
+      <right style="medium">
+        <color rgb="00C53030"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C53030"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C53030"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002A4365"/>
+      </left>
+      <right style="medium">
+        <color rgb="002A4365"/>
+      </right>
+      <top style="medium">
+        <color rgb="002A4365"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002A4365"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F6E2F"/>
+      </left>
+      <right style="medium">
+        <color rgb="002F6E2F"/>
+      </right>
+      <top style="medium">
+        <color rgb="002F6E2F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002F6E2F"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,6 +401,44 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,7 +833,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00CF3338"/>
+    <tabColor rgb="002A4365"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -662,46 +848,46 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Follow along — Your first PY() cell</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>This workbook teaches ONE lesson: where you place a PY() cell on the grid matters. Switch to the hello-world tab and follow the three steps below, in order. Steps 1 and 2 will work. Step 3 will fail — on purpose. That's the lesson.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>To insert a PY() cell:  Ctrl + Alt + Shift + P  (or Formulas tab → Insert Python)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Step 1 — Define a variable</t>
         </is>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>In cell B2 on the hello-world tab</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>my_object = 'Hello, world!'
 my_object</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>→ runs successfully. Shows 'Hello, world!' (as Python Object).</t>
         </is>
@@ -709,24 +895,24 @@
     </row>
     <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Step 2 — Reference it BELOW &amp; RIGHT</t>
         </is>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>In cell C3 on the hello-world tab</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>my_object</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>→ works. Python in Excel runs B2 first (above C3 in calc order), so my_object exists when C3 runs.</t>
         </is>
@@ -734,24 +920,24 @@
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3 — Reference it ABOVE — fails</t>
         </is>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>In cell A1 on the hello-world tab</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>my_object</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>→ FAILS with #PYTHON. A1 runs before B2 in calc order, so my_object doesn't exist yet. This is the gotcha.</t>
         </is>
@@ -759,14 +945,14 @@
     </row>
     <row r="13" ht="8" customHeight="1"/>
     <row r="15" ht="26" customHeight="1">
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>✓  Takeaway</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Python in Excel reads cells left-to-right, top-to-bottom — like reading a page. Put your definitions (imports, variables) in the top-left of the sheet and build DOWN and RIGHT. When you see #PYTHON on a cell that references a variable, check whether the cell DEFINING that variable is above or to the left of where you're using it.</t>
         </is>
@@ -791,7 +977,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E7D2E"/>
+    <tabColor rgb="002F6E2F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -801,61 +987,85 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="13" t="n"/>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="A1" s="29" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="31" t="inlineStr">
         <is>
           <t>← Step 3 goes in A1 (this WILL fail)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="15" t="n"/>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="A2" s="30" t="n"/>
+      <c r="B2" s="32" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>← Step 1 goes in B2 (the definition)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="A3" s="30" t="n"/>
+      <c r="B3" s="30" t="n"/>
+      <c r="C3" s="34" t="n"/>
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>← Step 2 goes in C3 (this works)</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="30" t="n"/>
+      <c r="B4" s="30" t="n"/>
+      <c r="C4" s="30" t="n"/>
+      <c r="D4" s="30" t="n"/>
+    </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Reminder:</t>
         </is>
       </c>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Python in Excel reads cells left-to-right, top-to-bottom.</t>
         </is>
       </c>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>A1 runs before B2 → A1 references something that doesn't exist yet → #PYTHON.</t>
         </is>
       </c>
+      <c r="B7" s="30" t="n"/>
+      <c r="C7" s="30" t="n"/>
+      <c r="D7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>B2 runs before C3 → C3 references something that already exists → works.</t>
         </is>
       </c>
+      <c r="B8" s="30" t="n"/>
+      <c r="C8" s="30" t="n"/>
+      <c r="D8" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
